--- a/delivrables/annex/2.1/Developments - Responses.xlsx
+++ b/delivrables/annex/2.1/Developments - Responses.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/FabioCruz/Documents/01-Projects/TechTraPlastiCE/techtraplastice/delivrables/annex/2.1/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D3F85C-F536-0E49-819F-3D9869D75B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Respuestas de formulario 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Respuestas de formulario 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="nwkIfjeKhAZKe3dLyeEpooe4YvkwhYz+4vfpH3xpoD8="/>
@@ -2063,28 +2072,34 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial (Corps)"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2092,7 +2107,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2114,131 +2129,198 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF5B3F86"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF5B3F86"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="21">
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial (Corps)"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="3" pivot="0" name="Respuestas de formulario 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Respuestas de formulario 1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="firstRowStripe" dxfId="19"/>
+      <tableStyleElement type="secondRowStripe" dxfId="18"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:O49" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:O49" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
   <tableColumns count="15">
-    <tableColumn name="Universidad/Institución" id="1"/>
-    <tableColumn name="Título corto en ESPAÑOL" id="2"/>
-    <tableColumn name="Título corto en INGLÉS" id="3"/>
-    <tableColumn name="Subtítulo en ESPAÑOL" id="4"/>
-    <tableColumn name="Subtítulo en INGLÉS" id="5"/>
-    <tableColumn name="Descripción en ESPAÑOL" id="6"/>
-    <tableColumn name="Descripción en INGLÉS" id="7"/>
-    <tableColumn name="Potenciales beneficios o impactos" id="8"/>
-    <tableColumn name="Potenciales beneficios o impactos en INGLÉS" id="9"/>
-    <tableColumn name="Nivel de Madurez Tecnológica (TRL - Technology Readiness Level)" id="10"/>
-    <tableColumn name="Resultados obtenidos hasta ahora" id="11"/>
-    <tableColumn name="Área de aplicación" id="12"/>
-    <tableColumn name="Foto representativa del desarrollo" id="13"/>
-    <tableColumn name="Palabras clave del desarrollo" id="14"/>
-    <tableColumn name="Contacto" id="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Universidad/Institución" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Título corto en ESPAÑOL" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Título corto en INGLÉS" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Subtítulo en ESPAÑOL" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Subtítulo en INGLÉS" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Descripción en ESPAÑOL" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Descripción en INGLÉS" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Potenciales beneficios o impactos" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Potenciales beneficios o impactos en INGLÉS" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Nivel de Madurez Tecnológica (TRL - Technology Readiness Level)" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Resultados obtenidos hasta ahora" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Área de aplicación" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Foto representativa del desarrollo" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Palabras clave del desarrollo" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Contacto" dataDxfId="3"/>
   </tableColumns>
-  <tableStyleInfo name="Respuestas de formulario 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Respuestas de formulario 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2428,3343 +2510,3329 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:O999"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="22.13"/>
-    <col customWidth="1" min="2" max="2" width="23.38"/>
-    <col customWidth="1" min="3" max="3" width="21.75"/>
-    <col customWidth="1" min="4" max="4" width="21.5"/>
-    <col customWidth="1" min="5" max="5" width="19.88"/>
-    <col customWidth="1" min="6" max="6" width="23.5"/>
-    <col customWidth="1" min="7" max="7" width="22.0"/>
-    <col customWidth="1" min="8" max="8" width="30.25"/>
-    <col customWidth="1" min="9" max="10" width="37.63"/>
-    <col customWidth="1" min="11" max="11" width="30.13"/>
-    <col customWidth="1" min="12" max="12" width="18.88"/>
-    <col customWidth="1" min="13" max="13" width="29.63"/>
-    <col customWidth="1" min="14" max="14" width="26.13"/>
-    <col customWidth="1" min="15" max="18" width="18.88"/>
+    <col min="1" max="1" width="14.5" style="6" customWidth="1"/>
+    <col min="2" max="2" width="17" style="6" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="21.5" style="6" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="23.5" style="6" customWidth="1"/>
+    <col min="7" max="7" width="22" style="6" customWidth="1"/>
+    <col min="8" max="8" width="30.1640625" style="6" customWidth="1"/>
+    <col min="9" max="10" width="37.6640625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="30.1640625" style="6" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="29.6640625" style="6" customWidth="1"/>
+    <col min="14" max="14" width="26.1640625" style="6" customWidth="1"/>
+    <col min="15" max="18" width="18.83203125" style="6" customWidth="1"/>
+    <col min="19" max="16384" width="12.6640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" s="3" customFormat="1" ht="28" x14ac:dyDescent="0.15">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:15" ht="224" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:15" ht="345" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>38</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:15" ht="224" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="1" t="s">
         <v>51</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:15" ht="224" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="1" t="s">
         <v>60</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:15" ht="280" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="1" t="s">
         <v>74</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:15" ht="182" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="1" t="s">
         <v>86</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:15" ht="319" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="1" t="s">
         <v>98</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:15" ht="238" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="1" t="s">
         <v>110</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:15" ht="70" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="1" t="s">
         <v>124</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="O10" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:15" ht="306" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="1" t="s">
         <v>138</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="O11" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:15" ht="280" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="1" t="s">
         <v>150</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="N12" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="O12" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:15" ht="293" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="1" t="s">
         <v>161</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="N13" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="O13" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:15" ht="252" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="1" t="s">
         <v>173</v>
       </c>
       <c r="J14" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="N14" s="4" t="s">
+      <c r="N14" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="O14" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:15" ht="252" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="1" t="s">
         <v>184</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="O15" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:15" ht="409.6" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="1" t="s">
         <v>196</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M16" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="N16" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="O16" s="4" t="s">
+      <c r="O16" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:15" ht="332" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="1" t="s">
         <v>208</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M17" s="6" t="s">
+      <c r="M17" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="N17" s="4" t="s">
+      <c r="N17" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="O17" s="4" t="s">
+      <c r="O17" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:15" ht="238" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="1" t="s">
         <v>218</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="M18" s="6" t="s">
+      <c r="M18" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="N18" s="4" t="s">
+      <c r="N18" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="O18" s="4" t="s">
+      <c r="O18" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:15" ht="238" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="1" t="s">
         <v>229</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="L19" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="M19" s="6" t="s">
+      <c r="M19" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="N19" s="4" t="s">
+      <c r="N19" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="O19" s="4" t="s">
+      <c r="O19" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:15" ht="182" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="1" t="s">
         <v>243</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L20" s="4" t="s">
+      <c r="L20" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="M20" s="6" t="s">
+      <c r="M20" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="N20" s="4" t="s">
+      <c r="N20" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="O20" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:15" ht="154" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="1" t="s">
         <v>252</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K21" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="L21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M21" s="6" t="s">
+      <c r="M21" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="N21" s="4" t="s">
+      <c r="N21" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="O21" s="4" t="s">
+      <c r="O21" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:15" ht="112" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="1" t="s">
         <v>261</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L22" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="M22" s="6" t="s">
+      <c r="M22" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="N22" s="4" t="s">
+      <c r="N22" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="O22" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:15" ht="238" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="1" t="s">
         <v>272</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="M23" s="6" t="s">
+      <c r="M23" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="N23" s="4" t="s">
+      <c r="N23" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="O23" s="4" t="s">
+      <c r="O23" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:15" ht="196" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="1" t="s">
         <v>285</v>
       </c>
       <c r="J24" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="K24" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="L24" s="4" t="s">
+      <c r="L24" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="M24" s="6" t="s">
+      <c r="M24" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="N24" s="4" t="s">
+      <c r="N24" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="O24" s="4" t="s">
+      <c r="O24" s="1" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:15" ht="238" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="1" t="s">
         <v>296</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="K25" s="4" t="s">
+      <c r="K25" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L25" s="4" t="s">
+      <c r="L25" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="M25" s="6" t="s">
+      <c r="M25" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="N25" s="4" t="s">
+      <c r="N25" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="O25" s="4" t="s">
+      <c r="O25" s="1" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:15" ht="266" x14ac:dyDescent="0.15">
+      <c r="A26" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="1" t="s">
         <v>308</v>
       </c>
       <c r="J26" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="K26" s="4" t="s">
+      <c r="K26" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L26" s="4" t="s">
+      <c r="L26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M26" s="6" t="s">
+      <c r="M26" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="N26" s="4" t="s">
+      <c r="N26" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="O26" s="4" t="s">
+      <c r="O26" s="1" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:15" ht="196" x14ac:dyDescent="0.15">
+      <c r="A27" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="1" t="s">
         <v>319</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K27" s="4" t="s">
+      <c r="K27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L27" s="4" t="s">
+      <c r="L27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M27" s="6" t="s">
+      <c r="M27" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="N27" s="4" t="s">
+      <c r="N27" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="O27" s="4" t="s">
+      <c r="O27" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:15" ht="168" x14ac:dyDescent="0.15">
+      <c r="A28" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="1" t="s">
         <v>330</v>
       </c>
       <c r="J28" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="K28" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L28" s="4" t="s">
+      <c r="L28" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="M28" s="6" t="s">
+      <c r="M28" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="N28" s="4" t="s">
+      <c r="N28" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="O28" s="4" t="s">
+      <c r="O28" s="1" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="4" t="s">
+    <row r="29" spans="1:15" ht="196" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="1" t="s">
         <v>342</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="K29" s="4" t="s">
+      <c r="K29" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L29" s="4" t="s">
+      <c r="L29" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="M29" s="6" t="s">
+      <c r="M29" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="N29" s="4" t="s">
+      <c r="N29" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="O29" s="4" t="s">
+      <c r="O29" s="1" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:15" ht="224" x14ac:dyDescent="0.15">
+      <c r="A30" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="1" t="s">
         <v>352</v>
       </c>
       <c r="J30" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="K30" s="4" t="s">
+      <c r="K30" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L30" s="4" t="s">
+      <c r="L30" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M30" s="6" t="s">
+      <c r="M30" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="N30" s="4" t="s">
+      <c r="N30" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="O30" s="4" t="s">
+      <c r="O30" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:15" ht="126" x14ac:dyDescent="0.15">
+      <c r="A31" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="1" t="s">
         <v>363</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="K31" s="4" t="s">
+      <c r="K31" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L31" s="4" t="s">
+      <c r="L31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M31" s="6" t="s">
+      <c r="M31" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="N31" s="4" t="s">
+      <c r="N31" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="O31" s="4" t="s">
+      <c r="O31" s="1" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:15" ht="168" x14ac:dyDescent="0.15">
+      <c r="A32" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" s="1" t="s">
         <v>374</v>
       </c>
       <c r="J32" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="K32" s="4" t="s">
+      <c r="K32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L32" s="4" t="s">
+      <c r="L32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M32" s="6" t="s">
+      <c r="M32" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="N32" s="4" t="s">
+      <c r="N32" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="O32" s="4" t="s">
+      <c r="O32" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:15" ht="196" x14ac:dyDescent="0.15">
+      <c r="A33" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" s="1" t="s">
         <v>383</v>
       </c>
       <c r="J33" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="K33" s="4" t="s">
+      <c r="K33" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="L33" s="4" t="s">
+      <c r="L33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M33" s="6" t="s">
+      <c r="M33" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="N33" s="4" t="s">
+      <c r="N33" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="O33" s="4" t="s">
+      <c r="O33" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:15" ht="168" x14ac:dyDescent="0.15">
+      <c r="A34" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="1" t="s">
         <v>394</v>
       </c>
       <c r="J34" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="K34" s="4" t="s">
+      <c r="K34" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L34" s="4" t="s">
+      <c r="L34" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M34" s="6" t="s">
+      <c r="M34" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="N34" s="4" t="s">
+      <c r="N34" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="O34" s="4" t="s">
+      <c r="O34" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:15" ht="210" x14ac:dyDescent="0.15">
+      <c r="A35" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="I35" s="4" t="s">
+      <c r="I35" s="1" t="s">
         <v>406</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="K35" s="4" t="s">
+      <c r="K35" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="L35" s="4" t="s">
+      <c r="L35" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M35" s="6" t="s">
+      <c r="M35" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="N35" s="4" t="s">
+      <c r="N35" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="O35" s="4" t="s">
+      <c r="O35" s="1" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:15" ht="238" x14ac:dyDescent="0.15">
+      <c r="A36" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" s="1" t="s">
         <v>418</v>
       </c>
       <c r="J36" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="K36" s="4" t="s">
+      <c r="K36" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="L36" s="4" t="s">
+      <c r="L36" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="M36" s="6" t="s">
+      <c r="M36" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="N36" s="4" t="s">
+      <c r="N36" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="O36" s="4" t="s">
+      <c r="O36" s="1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:15" ht="252" x14ac:dyDescent="0.15">
+      <c r="A37" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H37" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="I37" s="4" t="s">
+      <c r="I37" s="1" t="s">
         <v>431</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="K37" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="L37" s="4" t="s">
+      <c r="L37" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="M37" s="6" t="s">
+      <c r="M37" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N37" s="4" t="s">
+      <c r="N37" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="O37" s="4" t="s">
+      <c r="O37" s="1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="4" t="s">
+    <row r="38" spans="1:15" ht="238" x14ac:dyDescent="0.15">
+      <c r="A38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="I38" s="1" t="s">
         <v>442</v>
       </c>
       <c r="J38" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="K38" s="4" t="s">
+      <c r="K38" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="L38" s="4" t="s">
+      <c r="L38" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="M38" s="6" t="s">
+      <c r="M38" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N38" s="4" t="s">
+      <c r="N38" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="O38" s="4" t="s">
+      <c r="O38" s="1" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="4" t="s">
+    <row r="39" spans="1:15" ht="126" x14ac:dyDescent="0.15">
+      <c r="A39" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="H39" s="4" t="s">
+      <c r="H39" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="I39" s="4" t="s">
+      <c r="I39" s="1" t="s">
         <v>454</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="K39" s="4" t="s">
+      <c r="K39" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="L39" s="4" t="s">
+      <c r="L39" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="M39" s="6" t="s">
+      <c r="M39" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N39" s="4" t="s">
+      <c r="N39" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="O39" s="4" t="s">
+      <c r="O39" s="1" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="4" t="s">
+    <row r="40" spans="1:15" ht="196" x14ac:dyDescent="0.15">
+      <c r="A40" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I40" s="1" t="s">
         <v>467</v>
       </c>
       <c r="J40" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="K40" s="4" t="s">
+      <c r="K40" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="L40" s="4" t="s">
+      <c r="L40" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="M40" s="6" t="s">
+      <c r="M40" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N40" s="4" t="s">
+      <c r="N40" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="O40" s="4" t="s">
+      <c r="O40" s="1" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="4" t="s">
+    <row r="41" spans="1:15" ht="280" x14ac:dyDescent="0.15">
+      <c r="A41" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="H41" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="I41" s="4" t="s">
+      <c r="I41" s="1" t="s">
         <v>479</v>
       </c>
       <c r="J41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K41" s="4" t="s">
+      <c r="K41" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="L41" s="4" t="s">
+      <c r="L41" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="M41" s="6" t="s">
+      <c r="M41" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N41" s="4" t="s">
+      <c r="N41" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="O41" s="4" t="s">
+      <c r="O41" s="1" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="4" t="s">
+    <row r="42" spans="1:15" ht="280" x14ac:dyDescent="0.15">
+      <c r="A42" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H42" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="I42" s="4" t="s">
+      <c r="I42" s="1" t="s">
         <v>491</v>
       </c>
       <c r="J42" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="K42" s="4" t="s">
+      <c r="K42" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="L42" s="4" t="s">
+      <c r="L42" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="M42" s="6" t="s">
+      <c r="M42" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N42" s="4" t="s">
+      <c r="N42" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="O42" s="4" t="s">
+      <c r="O42" s="1" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="4" t="s">
+    <row r="43" spans="1:15" ht="332" x14ac:dyDescent="0.15">
+      <c r="A43" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H43" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="I43" s="4" t="s">
+      <c r="I43" s="1" t="s">
         <v>502</v>
       </c>
       <c r="J43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K43" s="4" t="s">
+      <c r="K43" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="L43" s="4" t="s">
+      <c r="L43" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="M43" s="6" t="s">
+      <c r="M43" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N43" s="4" t="s">
+      <c r="N43" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="O43" s="4" t="s">
+      <c r="O43" s="1" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="4" t="s">
+    <row r="44" spans="1:15" ht="210" x14ac:dyDescent="0.15">
+      <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="H44" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="I44" s="4" t="s">
+      <c r="I44" s="1" t="s">
         <v>513</v>
       </c>
       <c r="J44" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K44" s="4" t="s">
+      <c r="K44" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="L44" s="4" t="s">
+      <c r="L44" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="M44" s="6" t="s">
+      <c r="M44" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N44" s="4" t="s">
+      <c r="N44" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="O44" s="4" t="s">
+      <c r="O44" s="1" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="4" t="s">
+    <row r="45" spans="1:15" ht="210" x14ac:dyDescent="0.15">
+      <c r="A45" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="H45" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="I45" s="4" t="s">
+      <c r="I45" s="1" t="s">
         <v>524</v>
       </c>
       <c r="J45" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="K45" s="4" t="s">
+      <c r="K45" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="L45" s="4" t="s">
+      <c r="L45" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="M45" s="6" t="s">
+      <c r="M45" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N45" s="4" t="s">
+      <c r="N45" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="O45" s="4" t="s">
+      <c r="O45" s="1" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="4" t="s">
+    <row r="46" spans="1:15" ht="384" x14ac:dyDescent="0.15">
+      <c r="A46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="H46" s="4" t="s">
+      <c r="H46" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="I46" s="4" t="s">
+      <c r="I46" s="1" t="s">
         <v>535</v>
       </c>
       <c r="J46" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="K46" s="4" t="s">
+      <c r="K46" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="L46" s="4" t="s">
+      <c r="L46" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="M46" s="6" t="s">
+      <c r="M46" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N46" s="4" t="s">
+      <c r="N46" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="O46" s="4" t="s">
+      <c r="O46" s="1" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="4" t="s">
+    <row r="47" spans="1:15" ht="238" x14ac:dyDescent="0.15">
+      <c r="A47" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H47" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="I47" s="1" t="s">
         <v>547</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="K47" s="4" t="s">
+      <c r="K47" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="L47" s="4" t="s">
+      <c r="L47" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="M47" s="6" t="s">
+      <c r="M47" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N47" s="4" t="s">
+      <c r="N47" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="O47" s="4" t="s">
+      <c r="O47" s="1" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="4" t="s">
+    <row r="48" spans="1:15" ht="224" x14ac:dyDescent="0.15">
+      <c r="A48" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="H48" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="I48" s="4" t="s">
+      <c r="I48" s="1" t="s">
         <v>558</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="K48" s="4" t="s">
+      <c r="K48" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="L48" s="4" t="s">
+      <c r="L48" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="M48" s="6" t="s">
+      <c r="M48" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N48" s="4" t="s">
+      <c r="N48" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="O48" s="4" t="s">
+      <c r="O48" s="1" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="4" t="s">
+    <row r="49" spans="1:15" ht="196" x14ac:dyDescent="0.15">
+      <c r="A49" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="H49" s="4" t="s">
+      <c r="H49" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="I49" s="4" t="s">
+      <c r="I49" s="1" t="s">
         <v>569</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="K49" s="4" t="s">
+      <c r="K49" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="L49" s="4" t="s">
+      <c r="L49" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="M49" s="6" t="s">
+      <c r="M49" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="N49" s="4" t="s">
+      <c r="N49" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="O49" s="4" t="s">
+      <c r="O49" s="1" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="65" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="66" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="67" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="68" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="69" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="70" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="71" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="72" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="73" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="74" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="75" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="76" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="77" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="78" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="79" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="80" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="81" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="82" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="83" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="84" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="85" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="86" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="87" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="88" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="89" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="90" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="91" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="92" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="93" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="94" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="95" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="96" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="97" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="98" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="99" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="100" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="101" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="102" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="103" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="104" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="105" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="106" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="107" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="108" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="109" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="110" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="111" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="112" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="113" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="114" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="115" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="116" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="117" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="118" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="119" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="120" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="121" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="122" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="123" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="124" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="125" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="126" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="127" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="128" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="129" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="130" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="131" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="132" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="133" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="134" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="135" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="136" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="137" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="138" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="139" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="140" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="141" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="142" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="143" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="144" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="145" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="146" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="147" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="148" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="149" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="150" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="151" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="152" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="153" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="154" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="155" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="156" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="157" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="158" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="159" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="160" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="161" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="162" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="163" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="164" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="165" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="166" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="167" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="168" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="169" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="170" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="171" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="172" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="173" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="174" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="175" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="176" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="177" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="178" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="179" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="180" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="181" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="182" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="183" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="184" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="185" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="186" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="187" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="188" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="189" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="190" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="191" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="192" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="193" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="194" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="195" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="196" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="197" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="198" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="199" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="200" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="201" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="202" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="203" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="204" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="205" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="206" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="207" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="208" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="209" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="210" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="211" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="212" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="213" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="214" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="215" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="216" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="217" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="218" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="219" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="220" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="221" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="222" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="223" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="224" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="225" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="226" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="227" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="228" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="229" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="230" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="231" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="232" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="233" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="234" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="235" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="236" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="237" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="238" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="239" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="240" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="241" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="242" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="243" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="244" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="245" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="246" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="247" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="248" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="249" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="250" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="251" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="252" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="253" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="254" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="255" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="256" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="257" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="258" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="259" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="260" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="261" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="262" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="263" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="264" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="265" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="266" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="267" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="268" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="269" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="270" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="271" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="272" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="273" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="274" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="275" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="276" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="277" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="278" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="279" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="280" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="281" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="282" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="283" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="284" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="285" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="286" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="287" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="288" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="289" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="290" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="291" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="292" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="293" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="294" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="295" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="296" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="297" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="298" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="299" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="300" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="301" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="302" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="303" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="304" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="305" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="306" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="307" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="308" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="309" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="310" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="311" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="312" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="313" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="314" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="315" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="316" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="317" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="318" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="319" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="320" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="321" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="322" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="323" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="324" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="325" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="326" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="327" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="328" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="329" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="330" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="331" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="332" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="333" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="334" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="335" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="336" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="337" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="338" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="339" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="340" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="341" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="342" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="343" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="344" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="345" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="346" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="347" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="348" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="349" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="350" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="351" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="352" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="353" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="354" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="355" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="356" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="357" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="358" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="359" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="360" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="361" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="362" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="363" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="364" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="365" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="366" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="367" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="368" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="369" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="370" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="371" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="372" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="373" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="374" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="375" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="376" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="377" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="378" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="379" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="380" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="381" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="382" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="383" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="384" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="385" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="386" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="387" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="388" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="389" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="390" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="391" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="392" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="393" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="394" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="395" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="396" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="397" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="398" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="399" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="400" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="401" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="402" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="403" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="404" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="405" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="406" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="407" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="408" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="409" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="410" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="411" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="412" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="413" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="414" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="415" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="416" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="417" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="418" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="419" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="420" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="421" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="422" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="423" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="424" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="425" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="426" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="427" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="428" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="429" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="430" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="431" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="432" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="433" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="434" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="435" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="436" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="437" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="438" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="439" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="440" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="441" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="442" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="443" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="444" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="445" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="446" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="447" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="448" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="449" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="450" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="451" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="452" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="453" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="454" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="455" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="456" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="457" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="458" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="459" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="460" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="461" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="462" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="463" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="464" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="465" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="466" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="467" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="468" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="469" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="470" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="471" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="472" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="473" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="474" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="475" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="476" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="477" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="478" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="479" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="480" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="481" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="482" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="483" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="484" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="485" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="486" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="487" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="488" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="489" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="490" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="491" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="492" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="493" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="494" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="495" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="496" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="497" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="498" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="499" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="500" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="501" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="502" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="503" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="504" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="505" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="506" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="507" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="508" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="509" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="510" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="511" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="512" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="513" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="514" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="515" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="516" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="517" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="518" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="519" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="520" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="521" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="522" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="523" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="524" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="525" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="526" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="527" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="528" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="529" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="530" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="531" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="532" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="533" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="534" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="535" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="536" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="537" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="538" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="539" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="540" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="541" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="542" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="543" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="544" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="545" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="546" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="547" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="548" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="549" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="550" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="551" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="552" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="553" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="554" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="555" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="556" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="557" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="558" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="559" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="560" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="561" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="562" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="563" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="564" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="565" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="566" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="567" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="568" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="569" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="570" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="571" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="572" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="573" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="574" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="575" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="576" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="577" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="578" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="579" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="580" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="581" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="582" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="583" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="584" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="585" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="586" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="587" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="588" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="589" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="590" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="591" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="592" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="593" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="594" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="595" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="596" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="597" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="598" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="599" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="600" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="601" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="602" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="603" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="604" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="605" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="606" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="607" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="608" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="609" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="610" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="611" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="612" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="613" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="614" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="615" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="616" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="617" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="618" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="619" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="620" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="621" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="622" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="623" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="624" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="625" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="626" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="627" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="628" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="629" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="630" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="631" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="632" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="633" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="634" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="635" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="636" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="637" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="638" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="639" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="640" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="641" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="642" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="643" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="644" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="645" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="646" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="647" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="648" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="649" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="650" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="651" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="652" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="653" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="654" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="655" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="656" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="657" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="658" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="659" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="660" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="661" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="662" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="663" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="664" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="665" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="666" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="667" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="668" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="669" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="670" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="671" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="672" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="673" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="674" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="675" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="676" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="677" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="678" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="679" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="680" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="681" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="682" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="683" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="684" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="685" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="686" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="687" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="688" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="689" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="690" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="691" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="692" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="693" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="694" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="695" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="696" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="697" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="698" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="699" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="700" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="701" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="702" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="703" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="704" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="705" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="706" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="707" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="708" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="709" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="710" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="711" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="712" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="713" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="714" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="715" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="716" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="717" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="718" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="719" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="720" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="721" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="722" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="723" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="724" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="725" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="726" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="727" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="728" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="729" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="730" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="731" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="732" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="733" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="734" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="735" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="736" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="737" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="738" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="739" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="740" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="741" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="742" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="743" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="744" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="745" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="746" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="747" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="748" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="749" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="750" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="751" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="752" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="753" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="754" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="755" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="756" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="757" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="758" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="759" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="760" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="761" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="762" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="763" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="764" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="765" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="766" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="767" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="768" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="769" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="770" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="771" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="772" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="773" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="774" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="775" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="776" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="777" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="778" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="779" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="780" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="781" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="782" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="783" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="784" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="785" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="786" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="787" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="788" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="789" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="790" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="791" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="792" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="793" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="794" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="795" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="796" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="797" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="798" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="799" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="800" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="801" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="802" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="803" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="804" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="805" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="806" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="807" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="808" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="809" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="810" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="811" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="812" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="813" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="814" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="815" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="816" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="817" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="818" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="819" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="820" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="821" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="822" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="823" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="824" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="825" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="826" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="827" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="828" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="829" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="830" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="831" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="832" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="833" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="834" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="835" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="836" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="837" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="838" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="839" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="840" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="841" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="842" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="843" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="844" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="845" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="846" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="847" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="848" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="849" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="850" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="851" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="852" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="853" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="854" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="855" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="856" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="857" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="858" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="859" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="860" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="861" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="862" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="863" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="864" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="865" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="866" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="867" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="868" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="869" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="870" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="871" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="872" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="873" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="874" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="875" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="876" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="877" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="878" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="879" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="880" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="881" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="882" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="883" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="884" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="885" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="886" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="887" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="888" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="889" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="890" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="891" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="892" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="893" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="894" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="895" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="896" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="897" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="898" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="899" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="900" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="901" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="902" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="903" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="904" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="905" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="906" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="907" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="908" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="909" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="910" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="911" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="912" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="913" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="914" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="915" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="916" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="917" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="918" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="919" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="920" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="921" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="922" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="923" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="924" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="925" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="926" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="927" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="928" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="929" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="930" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="931" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="932" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="933" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="934" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="935" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="936" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="937" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="938" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="939" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="940" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="941" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="942" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="943" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="944" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="945" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="946" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="947" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="948" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="949" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="950" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="951" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="952" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="953" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="954" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="955" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="956" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="957" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="958" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="959" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="960" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="961" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="962" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="963" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="964" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="965" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="966" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="967" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="968" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="969" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="970" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="971" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="972" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="973" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="974" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="975" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="976" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="977" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="978" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="979" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="980" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="981" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="982" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="983" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="984" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="985" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="986" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="987" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="988" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="989" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="990" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="991" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="992" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="993" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="994" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="995" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="996" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="997" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="998" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="999" s="6" customFormat="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="M2"/>
-    <hyperlink r:id="rId2" ref="M3"/>
-    <hyperlink r:id="rId3" ref="M4"/>
-    <hyperlink r:id="rId4" ref="M5"/>
-    <hyperlink r:id="rId5" ref="M6"/>
-    <hyperlink r:id="rId6" ref="M7"/>
-    <hyperlink r:id="rId7" ref="M8"/>
-    <hyperlink r:id="rId8" ref="M9"/>
-    <hyperlink r:id="rId9" ref="M10"/>
-    <hyperlink r:id="rId10" ref="M11"/>
-    <hyperlink r:id="rId11" ref="M12"/>
-    <hyperlink r:id="rId12" ref="M13"/>
-    <hyperlink r:id="rId13" ref="M14"/>
-    <hyperlink r:id="rId14" ref="M15"/>
-    <hyperlink r:id="rId15" ref="M16"/>
-    <hyperlink r:id="rId16" ref="M17"/>
-    <hyperlink r:id="rId17" ref="M18"/>
-    <hyperlink r:id="rId18" ref="M19"/>
-    <hyperlink r:id="rId19" ref="M20"/>
-    <hyperlink r:id="rId20" ref="M21"/>
-    <hyperlink r:id="rId21" ref="M22"/>
-    <hyperlink r:id="rId22" ref="M23"/>
-    <hyperlink r:id="rId23" ref="M24"/>
-    <hyperlink r:id="rId24" ref="M25"/>
-    <hyperlink r:id="rId25" ref="M26"/>
-    <hyperlink r:id="rId26" ref="M27"/>
-    <hyperlink r:id="rId27" ref="M28"/>
-    <hyperlink r:id="rId28" ref="M29"/>
-    <hyperlink r:id="rId29" ref="M30"/>
-    <hyperlink r:id="rId30" ref="M31"/>
-    <hyperlink r:id="rId31" ref="M32"/>
-    <hyperlink r:id="rId32" ref="M33"/>
-    <hyperlink r:id="rId33" ref="M34"/>
-    <hyperlink r:id="rId34" ref="M35"/>
-    <hyperlink r:id="rId35" ref="M36"/>
-    <hyperlink r:id="rId36" ref="M37"/>
-    <hyperlink r:id="rId37" ref="M38"/>
-    <hyperlink r:id="rId38" ref="M39"/>
-    <hyperlink r:id="rId39" ref="M40"/>
-    <hyperlink r:id="rId40" ref="M41"/>
-    <hyperlink r:id="rId41" ref="M42"/>
-    <hyperlink r:id="rId42" ref="M43"/>
-    <hyperlink r:id="rId43" ref="M44"/>
-    <hyperlink r:id="rId44" ref="M45"/>
-    <hyperlink r:id="rId45" ref="M46"/>
-    <hyperlink r:id="rId46" ref="M47"/>
-    <hyperlink r:id="rId47" ref="M48"/>
-    <hyperlink r:id="rId48" ref="M49"/>
+    <hyperlink ref="M2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="M4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="M5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="M6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="M9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="M10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="M11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="M12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="M13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="M14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="M16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="M17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="M18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="M19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="M20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="M21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="M22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="M23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="M24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="M25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="M26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="M27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="M28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="M29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="M30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="M31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="M32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="M33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="M34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="M35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="M36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="M37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="M38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="M39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="M40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="M41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="M42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="M43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="M44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="M45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="M46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="M47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="M48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="M49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
   </hyperlinks>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId49"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup scale="39" fitToWidth="0" fitToHeight="0" orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId51"/>
+    <tablePart r:id="rId49"/>
   </tableParts>
 </worksheet>
 </file>